--- a/ig/DM-SIDOBA/ValueSet-jdv-j410-categorie-permis-conduire-ms.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-jdv-j410-categorie-permis-conduire-ms.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00.000+00:00</t>
+    <t>2026-06-01T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Catégorie de permis de conduire en France.</t>
+    <t>Catégorie de permis de conduire.</t>
   </si>
   <si>
     <t>Purpose</t>
